--- a/data/excel/attraction_transport_updated.xlsx
+++ b/data/excel/attraction_transport_updated.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$1</definedName>
-  </definedNames>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -23,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF305496"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,22 +46,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -215,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -285,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -416,46 +402,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -466,4131 +413,4080 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
-  <cols>
-    <col width="12" customWidth="1" style="1" min="1" max="1"/>
-    <col width="22" customWidth="1" style="1" min="2" max="2"/>
-    <col width="23" customWidth="1" style="1" min="3" max="3"/>
-    <col width="55" customWidth="1" style="1" min="4" max="4"/>
-    <col width="50" customWidth="1" style="1" min="5" max="5"/>
-    <col width="31" customWidth="1" style="1" min="6" max="6"/>
-    <col width="30" customWidth="1" style="1" min="7" max="7"/>
-    <col width="55" customWidth="1" style="1" min="8" max="8"/>
-    <col width="60" customWidth="1" style="1" min="9" max="9"/>
-  </cols>
+  <dimension ref="A1:H107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="1" s="2">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>id (主键)</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>attraction_id (对应景点)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>transport_type (交通类型)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>line_name (路线)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>low_floor_wheelchair_seat_available (低地板和轮椅座椅可用)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>boarding_point (长辈上车点)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>dropoff_point (下车站点)</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>walking_route (下车后步行指引)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>attraction_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>transport_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>line_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low_floor_wheelchair_seat_available</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>boarding_point</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dropoff_point</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>walking_route</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>2001</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" t="n">
         <v>101</v>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至澳门博物馆；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2002</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" t="n">
         <v>102</v>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>巴士：1、2、5、6B、10、10A、11、18、21A、26、55、60；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>妈阁站、妈阁总站或妈阁庙站</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>由妈阁站、妈阁总站或妈阁庙站出站，沿妈阁上街/妈阁斜巷按指示步行至澳门当代艺术中心．海事工房1号；优先选择有行人过路线段，避免走陡斜小巷。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2003</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" t="n">
         <v>501</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往澳门仁慈堂大楼；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>2004</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" t="n">
         <v>502</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至澳门文化中心；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2005</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" t="n">
         <v>503</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至澳门文学馆；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>2006</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" t="n">
         <v>504</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至澳门渔人码头；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>2007</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" t="n">
         <v>505</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至澳门中央图书馆；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>2008</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" t="n">
         <v>506</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往澳門仁慈堂大樓；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>2009</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" t="n">
         <v>507</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>巴士：8A、17、18、18A、19、26</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>白鸽巢公园站、连胜马路站或花王堂街站</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>由白鸽巢公园站或连胜马路站下车，沿公园前地/花王堂街步行至白鸽巢公园；园区周边有坡道和石阶，长者宜选择坡度较缓入口。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>2010</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" t="n">
         <v>508</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>巴士：8A、17、18、18A、19、26</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>白鸽巢公园站、连胜马路站或花王堂街站</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>由白鸽巢公园站或连胜马路站下车，沿公园前地/花王堂街步行至白鸽巢前地；园区周边有坡道和石阶，长者宜选择坡度较缓入口。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>2011</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" t="n">
         <v>103</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往板樟堂前地；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>2012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" t="n">
         <v>509</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往包公庙及医灵庙；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>2013</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" t="n">
         <v>301</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至兵房斜巷；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>2014</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" t="n">
         <v>104</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往彩虹屋及三幅壁画；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>2015</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" t="n">
         <v>510</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至城墙遗迹（圣方济各斜巷一段）；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>2016</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至大炮台（中央炮台）；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>2017</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" t="n">
         <v>511</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至大炮台陈列室；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>2018</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" t="n">
         <v>302</v>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H19" s="1" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至氹仔北帝庙；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>2019</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" t="n">
         <v>201</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至氹仔市政花园；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>2020</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" t="n">
         <v>202</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至氹仔天后古庙（天后宫）；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>2021</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" t="n">
         <v>512</v>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H22" s="1" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至得胜花园；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>2022</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" t="n">
         <v>106</v>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往典当业展示馆；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>2023</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" t="n">
         <v>513</v>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>巴士：8A、17、18、18A、19、26</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>白鸽巢公园站、连胜马路站或花王堂街站</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>由白鸽巢公园站或连胜马路站下车，沿公园前地/花王堂街步行至东方基金会会址（原贾梅士花园房屋旧址）；园区周边有坡道和石阶，长者宜选择坡度较缓入口。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>2024</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" t="n">
         <v>107</v>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至东望洋炮台、圣母雪地殿教堂及灯塔；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>2025</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" t="n">
         <v>108</v>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至東望洋炮台、聖母雪地殿教堂及燈塔；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>2026</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" t="n">
         <v>514</v>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至二龙喉公园；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>2027</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" t="n">
         <v>515</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至岗顶剧院；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>2028</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" t="n">
         <v>516</v>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至岗顶前地；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>2029</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" t="n">
         <v>517</v>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至崗頂前地；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>2030</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" t="n">
         <v>518</v>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至观音古庙及城隍庙；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>2031</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" t="n">
         <v>519</v>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至观音莲花苑；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>2032</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" t="n">
         <v>520</v>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至观音堂；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>2033</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" t="n">
         <v>109</v>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>巴士：1、2、5、6B、10、10A、11、18、21A、26、55、60；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>妈阁站、妈阁总站或妈阁庙站</t>
         </is>
       </c>
-      <c r="H34" s="1" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>由妈阁站、妈阁总站或妈阁庙站出站，沿妈阁上街/妈阁斜巷按指示步行至海事及水務局大樓（原摩爾兵營舊址）；优先选择有行人过路线段，避免走陡斜小巷。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>2034</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" t="n">
         <v>521</v>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H35" s="1" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至何東圖書館大樓；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>2035</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" t="n">
         <v>522</v>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至何贤公园；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>2036</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" t="n">
         <v>303</v>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至花城公园；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>2037</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" t="n">
         <v>523</v>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>巴士：1、3、3A、10、25、25B、30、34、AP1</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>台山街市站、李宝椿街站或纪念孙中山市政公园站</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>由台山街市站、李宝椿街站或纪念孙中山市政公园一带下车，沿有灯控路口的人行道步行至花地玛圣母堂；长者宜避开交通繁忙路口的急行。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>2038</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" t="n">
         <v>524</v>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至华士古达嘉马花园；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>2039</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" t="n">
         <v>525</v>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>巴士：8A、17、18、18A、19、26</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>白鸽巢公园站、连胜马路站或花王堂街站</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>由白鸽巢公园站或连胜马路站下车，沿公园前地/花王堂街步行至基督教墳場；园区周边有坡道和石阶，长者宜选择坡度较缓入口。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>2040</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" t="n">
         <v>304</v>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至计单奴街66号壁画；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>2041</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" t="n">
         <v>110</v>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>巴士：1、3、3A、10、25、25B、30、34、AP1</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>台山街市站、李宝椿街站或纪念孙中山市政公园站</t>
         </is>
       </c>
-      <c r="H42" s="1" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>由台山街市站、李宝椿街站或纪念孙中山市政公园一带下车，沿有灯控路口的人行道步行至纪念孙中山市政公园；长者宜避开交通繁忙路口的急行。</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>2042</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" t="n">
         <v>111</v>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至加思栏花园（南湾花园）；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>2043</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" t="n">
         <v>526</v>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至加思栏炮台；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>2044</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" t="n">
         <v>203</v>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H45" s="1" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至嘉模圣母堂；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>2045</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" t="n">
         <v>305</v>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或九澳方向巴士站点</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>九澳村站或九澳圣母村站</t>
         </is>
       </c>
-      <c r="H46" s="1" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>由九澳村站或九澳圣母村站下车，沿村内道路步行至九澳七苦圣母小堂；该区班次相对疏落，长者应先核实回程班次。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>2046</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" t="n">
         <v>527</v>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H47" s="1" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往俊秀围／俊秀里；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>2047</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" t="n">
         <v>306</v>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H48" s="1" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往康公庙；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>2048</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" t="n">
         <v>204</v>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H49" s="1" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往柯邦迪前地（司打口）；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>2049</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" t="n">
         <v>307</v>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H50" s="1" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至荔枝碗船厂片区；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>2050</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" t="n">
         <v>528</v>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H51" s="1" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至莲峰庙；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>2051</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" t="n">
         <v>205</v>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H52" s="1" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往莲溪庙；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>2052</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" t="n">
         <v>529</v>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H53" s="1" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往卢家大屋；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>2053</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" t="n">
         <v>112</v>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H54" s="1" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往卢廉若公园；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>2054</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" t="n">
         <v>113</v>
       </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H55" s="1" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往鲁班先师木工艺陈列馆；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>2055</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" t="n">
         <v>308</v>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H56" s="1" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至路环观音古庙；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>2056</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" t="n">
         <v>309</v>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至路环码头；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>2057</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" t="n">
         <v>310</v>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H58" s="1" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至路环三圣宫（金花庙）；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>2058</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" t="n">
         <v>311</v>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26、26A、50、N3；轻轨：石排湾线：石排湾站</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨石排湾线沿线车站</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>石排湾站、石排湾郊野公园站或石排湾马路站</t>
         </is>
       </c>
-      <c r="H59" s="1" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>由石排湾站或石排湾郊野公园站点下车，沿石排湾马路及园区入口步行至路环山顶公园和妈祖像；郊野公园及山路路段需留意坡度和遮阴。</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>2059</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" t="n">
         <v>312</v>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H60" s="1" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至路环圣方济各圣堂；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>2060</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" t="n">
         <v>313</v>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H61" s="1" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至路环天后古庙；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>2061</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" t="n">
         <v>314</v>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H62" s="1" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至路环图书馆；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>2062</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" t="n">
         <v>530</v>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H63" s="1" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至螺丝山公园；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>2063</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" t="n">
         <v>114</v>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>巴士：1、2、5、6B、10、10A、11、18、21A、26、55、60；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>妈阁站、妈阁总站或妈阁庙站</t>
         </is>
       </c>
-      <c r="H64" s="1" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>由妈阁站、妈阁总站或妈阁庙站出站，沿妈阁上街/妈阁斜巷按指示步行至妈阁庙前地壁画；优先选择有行人过路线段，避免走陡斜小巷。</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>2064</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" t="n">
         <v>115</v>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>巴士：1、2、5、6B、10、10A、11、18、21A、26、55、60；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>妈阁站、妈阁总站或妈阁庙站</t>
         </is>
       </c>
-      <c r="H65" s="1" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>由妈阁站、妈阁总站或妈阁庙站出站，沿妈阁上街/妈阁斜巷按指示步行至妈祖阁（妈阁庙）；优先选择有行人过路线段，避免走陡斜小巷。</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>2065</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" t="n">
         <v>116</v>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>巴士：1、2、5、6B、10、10A、11、18、21A、26、55、60；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>妈阁站、妈阁总站或妈阁庙站</t>
         </is>
       </c>
-      <c r="H66" s="1" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>由妈阁站、妈阁总站或妈阁庙站出站，沿妈阁上街/妈阁斜巷按指示步行至媽祖閣（媽閣廟）；优先选择有行人过路线段，避免走陡斜小巷。</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>2066</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" t="n">
         <v>531</v>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>巴士：8A、17、18、18A、19、26</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>白鸽巢公园站、连胜马路站或花王堂街站</t>
         </is>
       </c>
-      <c r="H67" s="1" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>由白鸽巢公园站或连胜马路站下车，沿公园前地/花王堂街步行至马礼逊教堂；园区周边有坡道和石阶，长者宜选择坡度较缓入口。</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>2067</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" t="n">
         <v>117</v>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H68" s="1" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往玫瑰圣母堂（板樟堂）；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>2068</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" t="n">
         <v>532</v>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H69" s="1" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往玫瑰聖母堂（板樟堂）；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>2069</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" t="n">
         <v>315</v>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H70" s="1" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至哪咤古庙（柿山）；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>2070</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" t="n">
         <v>118</v>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
         </is>
       </c>
-      <c r="H71" s="1" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至哪咤庙（大三巴）；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>2071</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" t="n">
         <v>119</v>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D72" s="1" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>巴士：1、2、5、6B、10、10A、11、18、21A、26、55、60；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E72" s="1" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F72" s="1" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>妈阁站、妈阁总站或妈阁庙站</t>
         </is>
       </c>
-      <c r="H72" s="1" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>由妈阁站、妈阁总站或妈阁庙站出站，沿妈阁上街/妈阁斜巷按指示步行至南光仓壁画；优先选择有行人过路线段，避免走陡斜小巷。</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>2072</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" t="n">
         <v>206</v>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>巴士：11、15、22、28A、30、33、34、MT4；轻轨：氹仔线：排角站、运动场站</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>排角站、运动场站、氹仔官也街站或嘉模泳池站</t>
         </is>
       </c>
-      <c r="H73" s="1" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>由排角站、运动场站或氹仔官也街站下车，沿嘉路士米耶马路/官也街周边步行至菩提禅院；旧城区路面较窄，长者宜靠边慢行。</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>2073</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" t="n">
         <v>533</v>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G74" s="1" t="inlineStr">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H74" s="1" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至饶宗颐学艺馆；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>2074</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" t="n">
         <v>207</v>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H75" s="1" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往仁慈堂博物馆；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>2075</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" t="n">
         <v>120</v>
       </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H76" s="1" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往三街会馆（关帝庙）；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>2076</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" t="n">
         <v>121</v>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H77" s="1" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往三街會館（關帝廟）；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>2077</v>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" t="n">
         <v>534</v>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D78" s="1" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26、26A、50、51A、MT4；轻轨：氹仔线：路氹东站、东亚运站、莲花站</t>
         </is>
       </c>
-      <c r="E78" s="1" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F78" s="1" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G78" s="1" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>路氹东站、东亚运站、莲花站或上葡京站</t>
         </is>
       </c>
-      <c r="H78" s="1" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>由路氹东站、东亚运站、莲花站或上葡京周边站点下车，按商场/度假村导向牌经室内通道或宽阔人行道前往上葡京艺术文化展馆；优先使用升降机。</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>2078</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" t="n">
         <v>122</v>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>巴士：8A、17、18、18A、19、26</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>白鸽巢公园站、连胜马路站或花王堂街站</t>
         </is>
       </c>
-      <c r="H79" s="1" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>由白鸽巢公园站或连胜马路站下车，沿公园前地/花王堂街步行至圣安多尼堂及前地（花王堂）；园区周边有坡道和石阶，长者宜选择坡度较缓入口。</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>2079</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" t="n">
         <v>535</v>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至圣奥斯定教堂；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>2080</v>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" t="n">
         <v>123</v>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
         </is>
       </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G81" s="1" t="inlineStr">
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
         </is>
       </c>
-      <c r="H81" s="1" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至圣保禄学院天主之母教堂遗址（大三巴牌坊、前地及石阶）；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>2081</v>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" t="n">
         <v>536</v>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E82" s="1" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H82" s="1" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至圣老楞佐堂及前地（风顺堂）；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>2082</v>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" t="n">
         <v>208</v>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H83" s="1" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至圣弥额尔小堂；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>2083</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" t="n">
         <v>124</v>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E84" s="1" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H84" s="1" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至圣若瑟修院藏珍馆；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>2084</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" t="n">
         <v>537</v>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H85" s="1" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至圣若瑟修院大楼、圣若瑟修院教堂、前地及石阶；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>2085</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" t="n">
         <v>538</v>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H86" s="1" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>由亚婆井前地站或风顺堂街站下车步行至聖奧斯定堂；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>2086</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" t="n">
         <v>316</v>
       </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H87" s="1" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至十月初五马路壁画；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>2087</v>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" t="n">
         <v>317</v>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D88" s="1" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26、26A、50、N3；轻轨：石排湾线：石排湾站</t>
         </is>
       </c>
-      <c r="E88" s="1" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F88" s="1" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或轻轨石排湾线沿线车站</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>石排湾站、石排湾郊野公园站或石排湾马路站</t>
         </is>
       </c>
-      <c r="H88" s="1" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>由石排湾站或石排湾郊野公园站点下车，沿石排湾马路及园区入口步行至石排湾郊野公园；郊野公园及山路路段需留意坡度和遮阴。</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>2088</v>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" t="n">
         <v>125</v>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H89" s="1" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至市政牧场旧址（牛房）；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>2089</v>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" t="n">
         <v>539</v>
       </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H90" s="1" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至宋玉生公园；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>2090</v>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" t="n">
         <v>318</v>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>巴士：15、21A、25、26A、50、N3</t>
         </is>
       </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
         </is>
       </c>
-      <c r="H91" s="1" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至谭公庙；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>2091</v>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" t="n">
         <v>319</v>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H92" s="1" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至通讯博物馆；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>2092</v>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" t="n">
         <v>540</v>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G93" s="1" t="inlineStr">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H93" s="1" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往同善堂历史档案陈列馆；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>2093</v>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" t="n">
         <v>541</v>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>巴士：2、2A、6A、6B、12、17、18、18A、19、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="inlineStr">
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>塔石体育馆站、荷兰园站、东望洋新街站或得胜花园站</t>
         </is>
       </c>
-      <c r="H94" s="1" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>由塔石体育馆站、荷兰园站或东望洋新街站下车，沿人行道及行人过路线步行至望德圣母堂；若目的地在东望洋山上，建议选择较平缓路线或改乘的士至山上入口附近。</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>2094</v>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" t="n">
         <v>542</v>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H95" s="1" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至望厦炮台；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>2095</v>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" t="n">
         <v>209</v>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="inlineStr">
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H96" s="1" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至望厦山市政公园；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>2096</v>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" t="n">
         <v>543</v>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H97" s="1" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至望厦圣方济各小堂；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>2097</v>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" t="n">
         <v>544</v>
       </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D98" s="1" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>巴士：1A、2A、7、8、12、18、18B、22、25、25B、28C</t>
         </is>
       </c>
-      <c r="E98" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F98" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>美副将马路站、望厦炮台站、观音堂站或高士德站</t>
         </is>
       </c>
-      <c r="H98" s="1" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>由美副将马路站、望厦炮台站或观音堂站下车，沿较宽人行道步行至冼星海纪念馆；过路时优先使用灯控路口。</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>2098</v>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" t="n">
         <v>545</v>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H99" s="1" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至冼星海纪念铜像；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>2099</v>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>546</v>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>非实体线下景点，不适用公共交通下车后步行指引。</t>
+      <c r="A100" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B100" t="n">
+        <v>547</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>公交车（巴士）；轻轨</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>亚婆井前地站、风顺堂街站或妈阁站</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>由亚婆井前地站或风顺堂街站下车步行至亞婆井前地；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>2100</v>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>547</v>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="A101" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B101" t="n">
+        <v>126</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至耶稣会纪念广场；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B102" t="n">
+        <v>548</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>巴士：8、12、17、18、18A、28C</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>水塘马路站、嚤啰园站或松山隧道站</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>由水塘马路站、嚤啰园站或松山隧道周边站点下车，沿人行道步行至伊斯兰清真寺及坟场；注意绕行车流较多路口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B103" t="n">
+        <v>549</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至艺园；注意大型路口等候时间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B104" t="n">
+        <v>127</v>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>公交车（巴士）；轻轨</t>
         </is>
       </c>
-      <c r="D101" s="1" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
         </is>
       </c>
-      <c r="E101" s="1" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
         </is>
       </c>
-      <c r="G101" s="1" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>亚婆井前地站、风顺堂街站或妈阁站</t>
         </is>
       </c>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>由亚婆井前地站或风顺堂街站下车步行至亞婆井前地；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>2101</v>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>巴士：2、3、3A、5、6A、8A、10、10A、17、18、18A、19、26A、33</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>白鸽巢公园站、高园街站、炮兵马路站或新马路/永亨站</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>由白鸽巢公园站、高园街站或新马路一带下车，沿大三巴街/炮兵马路方向步行至耶稣会纪念广场；该片区有斜路和石级，行动不便者建议改乘的士到较近入口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>2102</v>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>548</v>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>巴士：8、12、17、18、18A、28C</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>水塘马路站、嚤啰园站或松山隧道站</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>由水塘马路站、嚤啰园站或松山隧道周边站点下车，沿人行道步行至伊斯兰清真寺及坟场；注意绕行车流较多路口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>2103</v>
-      </c>
-      <c r="B104" s="1" t="n">
-        <v>549</v>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>由亚婆井前地站或风顺堂街站下车步行至郑家大屋；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B105" t="n">
+        <v>550</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
         </is>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
         </is>
       </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至艺园；注意大型路口等候时间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>2104</v>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）；轻轨</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>巴士：9、16、18、28B；轻轨：氹仔线：妈阁站</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>轻轨列车设轮椅位置，车站设升降机、斜坡道及导向设施；巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站、妈阁总站或轻轨氹仔线沿线车站</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>亚婆井前地站、风顺堂街站或妈阁站</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>由亚婆井前地站或风顺堂街站下车步行至郑家大屋；若由妈阁站前往，沿内港旧城区方向上行，长者需预留斜路体力。</t>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至中华民族雕塑园；注意大型路口等候时间。</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>2105</v>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>550</v>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>巴士：3A、8、10A、12、17S、23、32、56、AP1</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站、外港码头站或宋玉生广场周边站点</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>文化中心站、渔人码头站、宋玉生广场站或何贤公园站</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>由文化中心站、渔人码头站或宋玉生广场周边站点下车，沿冼星海大马路/孙逸仙大马路宽阔人行道步行至中华民族雕塑园；注意大型路口等候时间。</t>
+      <c r="A106" t="n">
+        <v>2106</v>
+      </c>
+      <c r="B106" t="n">
+        <v>320</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>巴士：15、21A、25、26A、50、N3</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至主教山小堂；村内街巷较窄，长者宜避开车辆会车位置。</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>2106</v>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>320</v>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>巴士：15、21A、25、26A、50、N3</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站、氹仔市区站点或路环方向巴士站点</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>路环市区站、路环居民大会堂站、路环码头站或十月初五马路站</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>由路环市区站、路环码头站或十月初五马路站下车，沿村内道路按指示步行至主教山小堂；村内街巷较窄，长者宜避开车辆会车位置。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A107" t="n">
         <v>2107</v>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B107" t="n">
         <v>551</v>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>公交车（巴士）</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>公交车（巴士）</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>巴士：2、3、3A、3X、4、5、6A、8A、10、10A、11、18、18A、19、21A、26A、33</t>
         </is>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>巴士低地板/轮椅座位按当日派车为准</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>亚马喇前地站、关闸总站或外港码头站</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>巴士低地板/轮椅座位按当日派车为准</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>亚马喇前地站、关闸总站或外港码头站</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>新马路/永亨站、议事亭前地站或亚马喇前地站</t>
         </is>
       </c>
-      <c r="H108" s="1" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>由新马路/永亨站或议事亭前地站下车，沿议事亭前地及周边步行街前往主教座堂（大堂）；石板路和人流较多，长者宜放慢步速。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>